--- a/database/event/3309/event_3309_evp_summary.xlsx
+++ b/database/event/3309/event_3309_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.976000000000001</v>
+        <v>10.1001</v>
       </c>
       <c r="C2" t="n">
-        <v>5.5974</v>
+        <v>5.667</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6087</v>
+        <v>3.58</v>
       </c>
       <c r="E2" t="n">
-        <v>9.976000000000001</v>
+        <v>10.1001</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1846</v>
+        <v>4.3087</v>
       </c>
       <c r="G2" t="n">
         <v>5.7914</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2753</v>
+        <v>4.7744</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4652</v>
+        <v>3.8698</v>
       </c>
       <c r="J2" t="n">
         <v>5.7914</v>
@@ -529,7 +529,7 @@
         <v>201</v>
       </c>
       <c r="M2" t="n">
-        <v>9.256600000000001</v>
+        <v>9.661200000000001</v>
       </c>
       <c r="N2" t="n">
         <v>352</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.2258</v>
+        <v>9.139699999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>4.6153</v>
+        <v>5.1281</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9017</v>
+        <v>3.1973</v>
       </c>
       <c r="E3" t="n">
-        <v>8.2258</v>
+        <v>9.139699999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1706</v>
+        <v>4.0844</v>
       </c>
       <c r="G3" t="n">
         <v>5.0553</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1706</v>
+        <v>4.1013</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1706</v>
+        <v>4.1013</v>
       </c>
       <c r="J3" t="n">
         <v>5.0553</v>
@@ -575,7 +575,7 @@
         <v>293</v>
       </c>
       <c r="M3" t="n">
-        <v>8.225899999999999</v>
+        <v>9.156600000000001</v>
       </c>
       <c r="N3" t="n">
         <v>410</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.939</v>
+        <v>7.9397</v>
       </c>
       <c r="C4" t="n">
-        <v>4.4544</v>
+        <v>4.4548</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7858</v>
+        <v>2.7193</v>
       </c>
       <c r="E4" t="n">
-        <v>7.939</v>
+        <v>7.9397</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5237</v>
+        <v>4.5244</v>
       </c>
       <c r="G4" t="n">
         <v>3.4153</v>
       </c>
       <c r="H4" t="n">
-        <v>5.6392</v>
+        <v>5.6423</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5708</v>
+        <v>4.5733</v>
       </c>
       <c r="J4" t="n">
         <v>3.4153</v>
@@ -621,7 +621,7 @@
         <v>201</v>
       </c>
       <c r="M4" t="n">
-        <v>7.9861</v>
+        <v>7.9886</v>
       </c>
       <c r="N4" t="n">
         <v>352</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.2926</v>
+        <v>6.7611</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5307</v>
+        <v>3.7935</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1207</v>
+        <v>2.2497</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2926</v>
+        <v>6.7611</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8087</v>
+        <v>2.055</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4839</v>
+        <v>4.7061</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8087</v>
+        <v>2.055</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0871</v>
+        <v>2.055</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4839</v>
+        <v>4.7061</v>
       </c>
       <c r="K5" t="n">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="L5" t="n">
-        <v>201</v>
+        <v>293</v>
       </c>
       <c r="M5" t="n">
-        <v>5.571</v>
+        <v>6.761100000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>352</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.1458</v>
+        <v>6.2926</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4483</v>
+        <v>3.5307</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0614</v>
+        <v>2.0631</v>
       </c>
       <c r="E6" t="n">
-        <v>6.1458</v>
+        <v>6.2926</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4397</v>
+        <v>3.8087</v>
       </c>
       <c r="G6" t="n">
-        <v>4.7061</v>
+        <v>2.4839</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4397</v>
+        <v>3.8087</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4397</v>
+        <v>3.0871</v>
       </c>
       <c r="J6" t="n">
-        <v>4.7061</v>
+        <v>2.4839</v>
       </c>
       <c r="K6" t="n">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="L6" t="n">
-        <v>293</v>
+        <v>201</v>
       </c>
       <c r="M6" t="n">
-        <v>6.1458</v>
+        <v>5.571</v>
       </c>
       <c r="N6" t="n">
-        <v>410</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7">
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.2329</v>
+        <v>5.1892</v>
       </c>
       <c r="C7" t="n">
-        <v>2.9361</v>
+        <v>2.9116</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6926</v>
+        <v>1.6235</v>
       </c>
       <c r="E7" t="n">
-        <v>5.2329</v>
+        <v>5.1892</v>
       </c>
       <c r="F7" t="n">
-        <v>3.9218</v>
+        <v>3.8781</v>
       </c>
       <c r="G7" t="n">
         <v>1.3111</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9218</v>
+        <v>3.8781</v>
       </c>
       <c r="I7" t="n">
         <v>3.9769</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.5861</v>
+        <v>5.0813</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5732</v>
+        <v>2.851</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4313</v>
+        <v>1.5805</v>
       </c>
       <c r="E8" t="n">
-        <v>4.5861</v>
+        <v>5.0813</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7664</v>
+        <v>3.2616</v>
       </c>
       <c r="G8" t="n">
         <v>1.8198</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7664</v>
+        <v>3.2616</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7793</v>
+        <v>3.289</v>
       </c>
       <c r="J8" t="n">
         <v>1.8198</v>
@@ -805,7 +805,7 @@
         <v>135</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5991</v>
+        <v>5.1088</v>
       </c>
       <c r="N8" t="n">
         <v>286</v>
@@ -814,231 +814,231 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.3968</v>
+        <v>4.4087</v>
       </c>
       <c r="C9" t="n">
-        <v>2.467</v>
+        <v>2.4736</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3548</v>
+        <v>1.3125</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3968</v>
+        <v>4.4087</v>
       </c>
       <c r="F9" t="n">
-        <v>4.3392</v>
+        <v>4.4087</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0576</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8972</v>
+        <v>4.6097</v>
       </c>
       <c r="I9" t="n">
-        <v>3.9693</v>
+        <v>4.6485</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0576</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>169</v>
+        <v>263</v>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.0269</v>
+        <v>4.6485</v>
       </c>
       <c r="N9" t="n">
-        <v>221</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.3561</v>
+        <v>4.3968</v>
       </c>
       <c r="C10" t="n">
-        <v>2.4441</v>
+        <v>2.467</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3384</v>
+        <v>1.3078</v>
       </c>
       <c r="E10" t="n">
-        <v>4.3561</v>
+        <v>4.3968</v>
       </c>
       <c r="F10" t="n">
-        <v>4.1092</v>
+        <v>4.3392</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2469</v>
+        <v>0.0576</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1401</v>
+        <v>4.8972</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1982</v>
+        <v>3.9693</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2469</v>
+        <v>0.0576</v>
       </c>
       <c r="K10" t="n">
-        <v>227</v>
+        <v>169</v>
       </c>
       <c r="L10" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="M10" t="n">
-        <v>4.4451</v>
+        <v>4.0269</v>
       </c>
       <c r="N10" t="n">
-        <v>310</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.1078</v>
+        <v>4.3266</v>
       </c>
       <c r="C11" t="n">
-        <v>2.3048</v>
+        <v>2.4276</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2381</v>
+        <v>1.2798</v>
       </c>
       <c r="E11" t="n">
-        <v>4.1078</v>
+        <v>4.3266</v>
       </c>
       <c r="F11" t="n">
-        <v>4.2225</v>
+        <v>4.0797</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1147</v>
+        <v>0.2469</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3178</v>
+        <v>4.094</v>
       </c>
       <c r="I11" t="n">
-        <v>4.3581</v>
+        <v>4.1982</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1147</v>
+        <v>0.2469</v>
       </c>
       <c r="K11" t="n">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="L11" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2434</v>
+        <v>4.4451</v>
       </c>
       <c r="N11" t="n">
-        <v>329</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.826</v>
+        <v>4.2366</v>
       </c>
       <c r="C12" t="n">
-        <v>2.1467</v>
+        <v>2.3771</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1243</v>
+        <v>1.244</v>
       </c>
       <c r="E12" t="n">
-        <v>3.826</v>
+        <v>4.2366</v>
       </c>
       <c r="F12" t="n">
-        <v>4.1298</v>
+        <v>4.3513</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3038</v>
+        <v>-0.1147</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1298</v>
+        <v>4.5197</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3473</v>
+        <v>4.5961</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3038</v>
+        <v>-0.1147</v>
       </c>
       <c r="K12" t="n">
-        <v>169</v>
+        <v>237</v>
       </c>
       <c r="L12" t="n">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0435</v>
+        <v>4.4814</v>
       </c>
       <c r="N12" t="n">
-        <v>221</v>
+        <v>329</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.8088</v>
+        <v>3.8546</v>
       </c>
       <c r="C13" t="n">
-        <v>2.137</v>
+        <v>2.1627</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1173</v>
+        <v>1.0918</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8088</v>
+        <v>3.8546</v>
       </c>
       <c r="F13" t="n">
-        <v>3.8088</v>
+        <v>4.1584</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.3038</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8088</v>
+        <v>4.1695</v>
       </c>
       <c r="I13" t="n">
-        <v>3.8265</v>
+        <v>3.3795</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.3038</v>
       </c>
       <c r="K13" t="n">
-        <v>263</v>
+        <v>169</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8265</v>
+        <v>3.0757</v>
       </c>
       <c r="N13" t="n">
-        <v>263</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14">
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.4712</v>
+        <v>3.4298</v>
       </c>
       <c r="C14" t="n">
-        <v>1.9476</v>
+        <v>1.9244</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9809</v>
+        <v>0.9225</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4712</v>
+        <v>3.4298</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7051</v>
+        <v>3.6637</v>
       </c>
       <c r="G14" t="n">
         <v>-0.2339</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7051</v>
+        <v>3.6637</v>
       </c>
       <c r="I14" t="n">
         <v>3.757</v>
@@ -1090,231 +1090,231 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.0146</v>
+        <v>3.1115</v>
       </c>
       <c r="C15" t="n">
-        <v>1.6914</v>
+        <v>1.7458</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7965</v>
+        <v>0.7957</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0146</v>
+        <v>3.1115</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3279</v>
+        <v>3.1115</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6867</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3279</v>
+        <v>3.1115</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8868</v>
+        <v>3.1377</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6867</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>151</v>
+        <v>207</v>
       </c>
       <c r="L15" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5735</v>
+        <v>3.1377</v>
       </c>
       <c r="N15" t="n">
-        <v>352</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.0042</v>
+        <v>3.0146</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6856</v>
+        <v>1.6914</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7923</v>
+        <v>0.7571</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0042</v>
+        <v>3.0146</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0042</v>
+        <v>2.3279</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.6867</v>
       </c>
       <c r="H16" t="n">
-        <v>3.0042</v>
+        <v>2.3279</v>
       </c>
       <c r="I16" t="n">
-        <v>3.0182</v>
+        <v>1.8868</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.6867</v>
       </c>
       <c r="K16" t="n">
-        <v>263</v>
+        <v>151</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="M16" t="n">
-        <v>3.0182</v>
+        <v>2.5735</v>
       </c>
       <c r="N16" t="n">
-        <v>263</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8828</v>
+        <v>2.993</v>
       </c>
       <c r="C17" t="n">
-        <v>1.6175</v>
+        <v>1.6793</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7432</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8828</v>
+        <v>2.993</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8594</v>
+        <v>2.993</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0234</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8594</v>
+        <v>2.993</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8861</v>
+        <v>3.0182</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0234</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="L17" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9095</v>
+        <v>3.0182</v>
       </c>
       <c r="N17" t="n">
-        <v>329</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.6823</v>
+        <v>2.8615</v>
       </c>
       <c r="C18" t="n">
-        <v>1.505</v>
+        <v>1.6055</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6622</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6823</v>
+        <v>2.8615</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4216</v>
+        <v>2.8381</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2607</v>
+        <v>0.0234</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4216</v>
+        <v>2.8381</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4216</v>
+        <v>2.8861</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2607</v>
+        <v>0.0234</v>
       </c>
       <c r="K18" t="n">
-        <v>117</v>
+        <v>237</v>
       </c>
       <c r="L18" t="n">
-        <v>293</v>
+        <v>92</v>
       </c>
       <c r="M18" t="n">
-        <v>2.6823</v>
+        <v>2.9095</v>
       </c>
       <c r="N18" t="n">
-        <v>410</v>
+        <v>329</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.3911</v>
+        <v>2.6823</v>
       </c>
       <c r="C19" t="n">
-        <v>1.3416</v>
+        <v>1.505</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5446</v>
+        <v>0.6247</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3911</v>
+        <v>2.6823</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3911</v>
+        <v>0.4216</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2.2607</v>
       </c>
       <c r="H19" t="n">
-        <v>2.3911</v>
+        <v>0.4216</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4023</v>
+        <v>0.4216</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2.2607</v>
       </c>
       <c r="K19" t="n">
-        <v>207</v>
+        <v>117</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="M19" t="n">
-        <v>2.4023</v>
+        <v>2.6823</v>
       </c>
       <c r="N19" t="n">
-        <v>207</v>
+        <v>410</v>
       </c>
     </row>
     <row r="20">
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.3316</v>
+        <v>2.3229</v>
       </c>
       <c r="C20" t="n">
-        <v>1.3082</v>
+        <v>1.3033</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5206</v>
+        <v>0.4815</v>
       </c>
       <c r="E20" t="n">
-        <v>2.3316</v>
+        <v>2.3229</v>
       </c>
       <c r="F20" t="n">
-        <v>2.3316</v>
+        <v>2.3229</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.3316</v>
+        <v>2.3229</v>
       </c>
       <c r="I20" t="n">
         <v>2.3425</v>
@@ -1376,7 +1376,7 @@
         <v>1.2371</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4693</v>
+        <v>0.4345</v>
       </c>
       <c r="E21" t="n">
         <v>2.2048</v>
@@ -1422,7 +1422,7 @@
         <v>1.2224</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4588</v>
+        <v>0.4241</v>
       </c>
       <c r="E22" t="n">
         <v>2.1787</v>
@@ -1468,7 +1468,7 @@
         <v>1.199</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4419</v>
+        <v>0.4074</v>
       </c>
       <c r="E23" t="n">
         <v>2.1369</v>
@@ -1504,185 +1504,185 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9036</v>
+        <v>2.1157</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0681</v>
+        <v>1.1871</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3476</v>
+        <v>0.399</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9036</v>
+        <v>2.1157</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9036</v>
+        <v>3.1157</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9036</v>
+        <v>3.1157</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9036</v>
+        <v>2.5254</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K24" t="n">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9036</v>
+        <v>1.5254</v>
       </c>
       <c r="N24" t="n">
-        <v>179</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.7908</v>
+        <v>1.975</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0048</v>
+        <v>1.1081</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3021</v>
+        <v>0.3429</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7908</v>
+        <v>1.975</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3057</v>
+        <v>1.975</v>
       </c>
       <c r="G25" t="n">
-        <v>2.0965</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3057</v>
+        <v>1.975</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3071</v>
+        <v>1.975</v>
       </c>
       <c r="J25" t="n">
-        <v>2.0965</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="L25" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.7894</v>
+        <v>1.975</v>
       </c>
       <c r="N25" t="n">
-        <v>286</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7642</v>
+        <v>1.847</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9899</v>
+        <v>1.0363</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2913</v>
+        <v>0.2919</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7642</v>
+        <v>1.847</v>
       </c>
       <c r="F26" t="n">
-        <v>2.7642</v>
+        <v>1.847</v>
       </c>
       <c r="G26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.7642</v>
+        <v>1.847</v>
       </c>
       <c r="I26" t="n">
-        <v>2.2405</v>
+        <v>1.8626</v>
       </c>
       <c r="J26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="L26" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.2405</v>
+        <v>1.8626</v>
       </c>
       <c r="N26" t="n">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.7439</v>
+        <v>1.8324</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9785</v>
+        <v>1.0281</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2831</v>
+        <v>0.2861</v>
       </c>
       <c r="E27" t="n">
-        <v>1.7439</v>
+        <v>1.8324</v>
       </c>
       <c r="F27" t="n">
-        <v>1.7439</v>
+        <v>-0.2641</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2.0965</v>
       </c>
       <c r="H27" t="n">
-        <v>1.7439</v>
+        <v>-0.2641</v>
       </c>
       <c r="I27" t="n">
-        <v>1.752</v>
+        <v>-0.2663</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2.0965</v>
       </c>
       <c r="K27" t="n">
-        <v>207</v>
+        <v>151</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="M27" t="n">
-        <v>1.752</v>
+        <v>1.8302</v>
       </c>
       <c r="N27" t="n">
-        <v>207</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28">
@@ -1698,7 +1698,7 @@
         <v>0.8236</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1716</v>
+        <v>0.1409</v>
       </c>
       <c r="E28" t="n">
         <v>1.4679</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.4213</v>
+        <v>1.4152</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7975</v>
+        <v>0.794</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1528</v>
+        <v>0.1199</v>
       </c>
       <c r="E29" t="n">
-        <v>1.4213</v>
+        <v>1.4152</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8167</v>
+        <v>0.8106</v>
       </c>
       <c r="G29" t="n">
         <v>0.6046</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8167</v>
+        <v>0.8106</v>
       </c>
       <c r="I29" t="n">
         <v>0.8243</v>
@@ -1790,7 +1790,7 @@
         <v>0.7831</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1425</v>
+        <v>0.1121</v>
       </c>
       <c r="E30" t="n">
         <v>1.3957</v>
@@ -1836,7 +1836,7 @@
         <v>0.7425</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1132</v>
+        <v>0.0833</v>
       </c>
       <c r="E31" t="n">
         <v>1.3233</v>
@@ -1882,7 +1882,7 @@
         <v>0.6261</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0294</v>
+        <v>0.0007</v>
       </c>
       <c r="E32" t="n">
         <v>1.1159</v>
@@ -1928,7 +1928,7 @@
         <v>0.5854</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0001</v>
+        <v>-0.0282</v>
       </c>
       <c r="E33" t="n">
         <v>1.0434</v>
@@ -1964,78 +1964,78 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9569</v>
+        <v>0.972</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5369</v>
+        <v>0.5454</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0348</v>
+        <v>-0.0567</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9569</v>
+        <v>0.972</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9569</v>
+        <v>1.401</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.429</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9569</v>
+        <v>1.401</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9569</v>
+        <v>1.4247</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.429</v>
       </c>
       <c r="K34" t="n">
-        <v>124</v>
+        <v>237</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9569</v>
+        <v>0.9957</v>
       </c>
       <c r="N34" t="n">
-        <v>124</v>
+        <v>329</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.947</v>
+        <v>0.9569</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5313</v>
+        <v>0.5369</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0388</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>0.947</v>
+        <v>0.9569</v>
       </c>
       <c r="F35" t="n">
-        <v>0.947</v>
+        <v>0.9569</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.947</v>
+        <v>0.9569</v>
       </c>
       <c r="I35" t="n">
-        <v>0.947</v>
+        <v>0.9569</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.947</v>
+        <v>0.9569</v>
       </c>
       <c r="N35" t="n">
         <v>124</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8456</v>
+        <v>0.947</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4745</v>
+        <v>0.5313</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0798</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8456</v>
+        <v>0.947</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8456</v>
+        <v>0.947</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8456</v>
+        <v>0.947</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8456</v>
+        <v>0.947</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8456</v>
+        <v>0.947</v>
       </c>
       <c r="N36" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.838</v>
+        <v>0.8456</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4702</v>
+        <v>0.4745</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0828</v>
+        <v>-0.107</v>
       </c>
       <c r="E37" t="n">
-        <v>0.838</v>
+        <v>0.8456</v>
       </c>
       <c r="F37" t="n">
-        <v>1.267</v>
+        <v>0.8456</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.429</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.267</v>
+        <v>0.8456</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2789</v>
+        <v>0.8456</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.429</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>237</v>
+        <v>106</v>
       </c>
       <c r="L37" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8498999999999999</v>
+        <v>0.8456</v>
       </c>
       <c r="N37" t="n">
-        <v>329</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38">
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7948</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4459</v>
+        <v>0.4364</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1003</v>
+        <v>-0.1341</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7948</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>1.5384</v>
+        <v>1.5213</v>
       </c>
       <c r="G38" t="n">
         <v>-0.7436</v>
       </c>
       <c r="H38" t="n">
-        <v>1.5384</v>
+        <v>1.5213</v>
       </c>
       <c r="I38" t="n">
         <v>1.56</v>
@@ -2204,7 +2204,7 @@
         <v>0.4038</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1307</v>
+        <v>-0.1572</v>
       </c>
       <c r="E39" t="n">
         <v>0.7196</v>
@@ -2250,7 +2250,7 @@
         <v>0.402</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1319</v>
+        <v>-0.1585</v>
       </c>
       <c r="E40" t="n">
         <v>0.7165</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7024</v>
+        <v>0.6998</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3941</v>
+        <v>0.3926</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1376</v>
+        <v>-0.1651</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7024</v>
+        <v>0.6998</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7024</v>
+        <v>0.6998</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.7024</v>
+        <v>0.6998</v>
       </c>
       <c r="I41" t="n">
         <v>0.7057</v>
@@ -2342,7 +2342,7 @@
         <v>0.2784</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2209</v>
+        <v>-0.2462</v>
       </c>
       <c r="E42" t="n">
         <v>0.4962</v>
@@ -2388,7 +2388,7 @@
         <v>0.2616</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.233</v>
+        <v>-0.2582</v>
       </c>
       <c r="E43" t="n">
         <v>0.4662</v>
@@ -2434,7 +2434,7 @@
         <v>0.2309</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2551</v>
+        <v>-0.28</v>
       </c>
       <c r="E44" t="n">
         <v>0.4115</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.3938</v>
+        <v>0.3808</v>
       </c>
       <c r="C45" t="n">
-        <v>0.221</v>
+        <v>0.2137</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2623</v>
+        <v>-0.2922</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3938</v>
+        <v>0.3808</v>
       </c>
       <c r="F45" t="n">
-        <v>1.1662</v>
+        <v>1.1532</v>
       </c>
       <c r="G45" t="n">
         <v>-0.7724</v>
       </c>
       <c r="H45" t="n">
-        <v>1.1662</v>
+        <v>1.1532</v>
       </c>
       <c r="I45" t="n">
         <v>1.1826</v>
@@ -2526,7 +2526,7 @@
         <v>0.1973</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2793</v>
+        <v>-0.3038</v>
       </c>
       <c r="E46" t="n">
         <v>0.3516</v>
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.1539</v>
+        <v>0.2138</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0864</v>
+        <v>0.12</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3592</v>
+        <v>-0.3587</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1539</v>
+        <v>0.2138</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2913</v>
+        <v>0.3512</v>
       </c>
       <c r="G47" t="n">
         <v>-0.1374</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2913</v>
+        <v>0.3512</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2927</v>
+        <v>0.3542</v>
       </c>
       <c r="J47" t="n">
         <v>-0.1374</v>
@@ -2599,7 +2599,7 @@
         <v>135</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1553</v>
+        <v>0.2168</v>
       </c>
       <c r="N47" t="n">
         <v>286</v>
@@ -2618,7 +2618,7 @@
         <v>0.0861</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3594</v>
+        <v>-0.3828</v>
       </c>
       <c r="E48" t="n">
         <v>0.1535</v>
@@ -2654,32 +2654,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.133</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0542</v>
+        <v>0.0746</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3823</v>
+        <v>-0.3909</v>
       </c>
       <c r="E49" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.133</v>
       </c>
       <c r="F49" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.133</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.133</v>
       </c>
       <c r="I49" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.133</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.133</v>
       </c>
       <c r="N49" t="n">
         <v>179</v>
@@ -2700,32 +2700,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0931</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0522</v>
+        <v>0.0542</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3838</v>
+        <v>-0.4054</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0931</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0931</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0931</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0931</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.0931</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="N50" t="n">
         <v>179</v>
@@ -2756,7 +2756,7 @@
         <v>0.0472</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3874</v>
+        <v>-0.4104</v>
       </c>
       <c r="E51" t="n">
         <v>0.08409999999999999</v>
@@ -2802,7 +2802,7 @@
         <v>0.0462</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3881</v>
+        <v>-0.4111</v>
       </c>
       <c r="E52" t="n">
         <v>0.0823</v>
@@ -2848,7 +2848,7 @@
         <v>-0.0169</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4336</v>
+        <v>-0.4559</v>
       </c>
       <c r="E53" t="n">
         <v>-0.0302</v>
@@ -2894,7 +2894,7 @@
         <v>-0.0254</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4396</v>
+        <v>-0.4619</v>
       </c>
       <c r="E54" t="n">
         <v>-0.0452</v>
@@ -2940,7 +2940,7 @@
         <v>-0.0641</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4675</v>
+        <v>-0.4894</v>
       </c>
       <c r="E55" t="n">
         <v>-0.1142</v>
@@ -2986,7 +2986,7 @@
         <v>-0.0839</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4818</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="E56" t="n">
         <v>-0.1496</v>
@@ -3032,7 +3032,7 @@
         <v>-0.1185</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5067</v>
+        <v>-0.5281</v>
       </c>
       <c r="E57" t="n">
         <v>-0.2112</v>
@@ -3078,7 +3078,7 @@
         <v>-0.1322</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="E58" t="n">
         <v>-0.2357</v>
@@ -3124,7 +3124,7 @@
         <v>-0.1563</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5339</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="E59" t="n">
         <v>-0.2786</v>
@@ -3170,7 +3170,7 @@
         <v>-0.1662</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.541</v>
+        <v>-0.5619</v>
       </c>
       <c r="E60" t="n">
         <v>-0.2962</v>
@@ -3216,7 +3216,7 @@
         <v>-0.1674</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5419</v>
+        <v>-0.5628</v>
       </c>
       <c r="E61" t="n">
         <v>-0.2983</v>
@@ -3262,7 +3262,7 @@
         <v>-0.2494</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6009</v>
+        <v>-0.621</v>
       </c>
       <c r="E62" t="n">
         <v>-0.4445</v>
@@ -3308,7 +3308,7 @@
         <v>-0.253</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6036</v>
+        <v>-0.6236</v>
       </c>
       <c r="E63" t="n">
         <v>-0.451</v>
@@ -3354,7 +3354,7 @@
         <v>-0.2895</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6298</v>
+        <v>-0.6495</v>
       </c>
       <c r="E64" t="n">
         <v>-0.516</v>
@@ -3394,28 +3394,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.5647</v>
+        <v>-0.5305</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.3168</v>
+        <v>-0.2977</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6495</v>
+        <v>-0.6553</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.5647</v>
+        <v>-0.5305</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.5647</v>
+        <v>-0.5305</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.5647</v>
+        <v>-0.5305</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5674</v>
+        <v>-0.535</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.5674</v>
+        <v>-0.535</v>
       </c>
       <c r="N65" t="n">
         <v>207</v>
@@ -3446,7 +3446,7 @@
         <v>-0.4539</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7481</v>
+        <v>-0.7662</v>
       </c>
       <c r="E66" t="n">
         <v>-0.8089</v>
@@ -3492,7 +3492,7 @@
         <v>-0.679</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9103</v>
+        <v>-0.9261</v>
       </c>
       <c r="E67" t="n">
         <v>-1.2102</v>
@@ -3538,7 +3538,7 @@
         <v>-0.7284</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9458</v>
+        <v>-0.9611</v>
       </c>
       <c r="E68" t="n">
         <v>-1.2982</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.3055</v>
+        <v>-1.3007</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.7325</v>
+        <v>-0.7298</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9488</v>
+        <v>-0.9621</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.3055</v>
+        <v>-1.3007</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.3055</v>
+        <v>-1.3007</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.3055</v>
+        <v>-1.3007</v>
       </c>
       <c r="I69" t="n">
         <v>-1.3116</v>
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.3098</v>
+        <v>-1.3049</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.7349</v>
+        <v>-0.7322</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9505</v>
+        <v>-0.9638</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.3098</v>
+        <v>-1.3049</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.3098</v>
+        <v>-1.3049</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.3098</v>
+        <v>-1.3049</v>
       </c>
       <c r="I70" t="n">
         <v>-1.3159</v>
@@ -3676,7 +3676,7 @@
         <v>-0.7442</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="E71" t="n">
         <v>-1.3263</v>
@@ -3722,7 +3722,7 @@
         <v>-0.7726</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9776</v>
+        <v>-0.9925</v>
       </c>
       <c r="E72" t="n">
         <v>-1.377</v>
@@ -3768,7 +3768,7 @@
         <v>-0.792</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9916</v>
+        <v>-1.0063</v>
       </c>
       <c r="E73" t="n">
         <v>-1.4116</v>
@@ -3814,7 +3814,7 @@
         <v>-0.8187</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0108</v>
+        <v>-1.0253</v>
       </c>
       <c r="E74" t="n">
         <v>-1.4592</v>
@@ -3860,7 +3860,7 @@
         <v>-0.8303</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0192</v>
+        <v>-1.0335</v>
       </c>
       <c r="E75" t="n">
         <v>-1.4799</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.7389</v>
+        <v>-1.7391</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.9757</v>
+        <v>-0.9758</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1238</v>
+        <v>-1.1368</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.7389</v>
+        <v>-1.7391</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0428</v>
+        <v>0.0426</v>
       </c>
       <c r="G76" t="n">
         <v>-1.7817</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0428</v>
+        <v>0.0426</v>
       </c>
       <c r="I76" t="n">
         <v>0.043</v>
@@ -3952,7 +3952,7 @@
         <v>-1.0077</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1469</v>
+        <v>-1.1594</v>
       </c>
       <c r="E77" t="n">
         <v>-1.796</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.0611</v>
+        <v>-2.0485</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.1564</v>
+        <v>-1.1494</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.254</v>
+        <v>-1.26</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.0611</v>
+        <v>-2.0485</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.6934</v>
+        <v>-1.6808</v>
       </c>
       <c r="G78" t="n">
         <v>-0.3677</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.6934</v>
+        <v>-1.6808</v>
       </c>
       <c r="I78" t="n">
         <v>-1.7092</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.2909</v>
+        <v>-2.2864</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.2854</v>
+        <v>-1.2829</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3468</v>
+        <v>-1.3548</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.2909</v>
+        <v>-2.2864</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.21</v>
+        <v>-1.2055</v>
       </c>
       <c r="G79" t="n">
         <v>-1.0809</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.21</v>
+        <v>-1.2055</v>
       </c>
       <c r="I79" t="n">
         <v>-1.2156</v>
@@ -4090,7 +4090,7 @@
         <v>-1.3532</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3957</v>
+        <v>-1.4048</v>
       </c>
       <c r="E80" t="n">
         <v>-2.4118</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.1117</v>
+        <v>-3.1001</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.7459</v>
+        <v>-1.7394</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.6784</v>
+        <v>-1.679</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.1117</v>
+        <v>-3.1001</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.1117</v>
+        <v>-3.1001</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.1117</v>
+        <v>-3.1001</v>
       </c>
       <c r="I81" t="n">
         <v>-3.1262</v>
